--- a/index.xlsx
+++ b/index.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22575" windowHeight="10170"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="88">
   <si>
     <t>#</t>
   </si>
@@ -256,6 +256,51 @@
   </si>
   <si>
     <t>250718#000374L5-1</t>
+  </si>
+  <si>
+    <t>230505#GUANYI-TG-BAK-312G</t>
+  </si>
+  <si>
+    <t>230505 Camera Video 
+Channel 监控备份</t>
+  </si>
+  <si>
+    <t>312 GB</t>
+  </si>
+  <si>
+    <t>250718#000141L5-1</t>
+  </si>
+  <si>
+    <t>1095 GB</t>
+  </si>
+  <si>
+    <t>6aec5f0080437e7ee38bab6969065d8786326342f9b6342b24b214e9b2d057e0</t>
+  </si>
+  <si>
+    <t>220711#GUANYI-TG-BAK-2-PART1-424G</t>
+  </si>
+  <si>
+    <t>220711 部分视频TG云存储
+监控备份 第一部分</t>
+  </si>
+  <si>
+    <t>424 GB</t>
+  </si>
+  <si>
+    <t>5b5912cdfa5c4d7e10e4095321e46dda78bdc3296293b26e62bf0a5a66e3f5a7</t>
+  </si>
+  <si>
+    <t>250728#HOME-CAMERA-BAK-1-359G</t>
+  </si>
+  <si>
+    <t>250728-250901
+家庭监控视频备份</t>
+  </si>
+  <si>
+    <t>359 GB</t>
+  </si>
+  <si>
+    <t>67663c816a0cffbb9b69d875310a65cfb1a0142812b12e9d7074859a074e3baa</t>
   </si>
 </sst>
 </file>
@@ -1966,42 +2011,94 @@
       <c r="K17" s="4"/>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="4"/>
+      <c r="A18" s="4">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I18" s="5">
+        <v>45892</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="K18" s="4"/>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="4"/>
+      <c r="A19" s="4">
+        <v>13</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="G19" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="4"/>
+      <c r="I19" s="5">
+        <v>45901</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="K19" s="4"/>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="4"/>
+      <c r="A20" s="4">
+        <v>14</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="G20" s="4" t="s">
+        <v>86</v>
+      </c>
       <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="4"/>
+      <c r="I20" s="5">
+        <v>45901</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>87</v>
+      </c>
       <c r="K20" s="4"/>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11">
@@ -5159,7 +5256,7 @@
     </row>
     <row r="278" ht="36" customHeight="1"/>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="27">
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B10:B11"/>
@@ -5177,11 +5274,13 @@
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="F15:F16"/>
+    <mergeCell ref="F18:F20"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H18:H20"/>
     <mergeCell ref="I3:I5"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="I9:I10"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="96">
   <si>
     <t>#</t>
   </si>
@@ -301,6 +301,32 @@
   </si>
   <si>
     <t>67663c816a0cffbb9b69d875310a65cfb1a0142812b12e9d7074859a074e3baa</t>
+  </si>
+  <si>
+    <t>260123#JIGE-NVME-1T</t>
+  </si>
+  <si>
+    <t>机械革命 1T 系统盘备份
+系统盘备份数据日期
+2026-01-23</t>
+  </si>
+  <si>
+    <t>560 GB</t>
+  </si>
+  <si>
+    <t>250718#000197L5-1</t>
+  </si>
+  <si>
+    <t>541 GB</t>
+  </si>
+  <si>
+    <t>1500 GB</t>
+  </si>
+  <si>
+    <t>bec0d39515fe7e5e676cf6787921dbc5354b4659c0b872adf4abfa13d27be036</t>
+  </si>
+  <si>
+    <t>793 GB</t>
   </si>
 </sst>
 </file>
@@ -2101,29 +2127,55 @@
       </c>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" ht="36" customHeight="1" spans="1:11">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="4"/>
+    <row r="21" ht="65" customHeight="1" spans="1:11">
+      <c r="A21" s="4">
+        <v>15</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="5">
+        <v>46045</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="K21" s="4"/>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11">
-      <c r="A22" s="4"/>
+      <c r="A22" s="4">
+        <v>16</v>
+      </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="5"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="G22" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
+      <c r="I22" s="5">
+        <v>46045</v>
+      </c>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
@@ -3284,7 +3336,7 @@
       <c r="J111" s="7"/>
       <c r="K111" s="4"/>
     </row>
-    <row r="112" ht="36" customHeight="1" spans="1:10">
+    <row r="112" ht="36" customHeight="1" spans="1:11">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -5012,7 +5064,7 @@
       <c r="I255" s="5"/>
       <c r="J255" s="7"/>
     </row>
-    <row r="256" ht="36" customHeight="1" spans="1:9">
+    <row r="256" ht="36" customHeight="1" spans="1:10">
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -5256,7 +5308,7 @@
     </row>
     <row r="278" ht="36" customHeight="1"/>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B10:B11"/>
@@ -5281,6 +5333,7 @@
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="H18:H20"/>
+    <mergeCell ref="H21:H22"/>
     <mergeCell ref="I3:I5"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="I9:I10"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="110">
   <si>
     <t>#</t>
   </si>
@@ -62,7 +62,7 @@
     <t>其他</t>
   </si>
   <si>
-    <t>240825#ST4000NE001-HDD-4T-2</t>
+    <t>240825#ST4000NE001-HDD-2-4T</t>
   </si>
   <si>
     <t>最常用 4T 机械备份</t>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t>OnePlus Ace 3
-手机数据备份</t>
+手机第 1 次数据备份</t>
   </si>
   <si>
     <t>289 GB</t>
@@ -125,7 +125,7 @@
     <t>94f2c6df42d6dfcd2981c05425f293bf178dd56237c2e5c0c9efb6397efe8791</t>
   </si>
   <si>
-    <t>250223#ST4000NE001-HDD-4T-3</t>
+    <t>250223#ST4000NE001-HDD-3-4T</t>
   </si>
   <si>
     <t>4T 机械冷备盘
@@ -158,7 +158,7 @@
     <t>b7fbcefb1f90f3bba20a1928967a795360710b298da12e8a9ce3d6482ce1ce70</t>
   </si>
   <si>
-    <t>250223#ST4000NE001-HDD-4T-1</t>
+    <t>250223#ST4000NE001-HDD-1-4T</t>
   </si>
   <si>
     <t>台式 4T 机械备份</t>
@@ -311,22 +311,68 @@
 2026-01-23</t>
   </si>
   <si>
-    <t>560 GB</t>
+    <t>541 GB</t>
   </si>
   <si>
     <t>250718#000197L5-1</t>
   </si>
   <si>
-    <t>541 GB</t>
-  </si>
-  <si>
-    <t>1500 GB</t>
-  </si>
-  <si>
     <t>bec0d39515fe7e5e676cf6787921dbc5354b4659c0b872adf4abfa13d27be036</t>
   </si>
   <si>
-    <t>793 GB</t>
+    <t>260124#ONEPLUSACE3-UFS-512G-2</t>
+  </si>
+  <si>
+    <t>OnePlus Ace 3
+手机第 2 次数据备份</t>
+  </si>
+  <si>
+    <t>* 15</t>
+  </si>
+  <si>
+    <t>250718#000108L5-1</t>
+  </si>
+  <si>
+    <t>* 16</t>
+  </si>
+  <si>
+    <t>260124#ST4000NE001-HDD-2-4T-2</t>
+  </si>
+  <si>
+    <t>最常用 4T 机械第 2 次备份</t>
+  </si>
+  <si>
+    <t>3228 GB</t>
+  </si>
+  <si>
+    <t>250718#000335L5-1</t>
+  </si>
+  <si>
+    <t>250718#000383L5-1</t>
+  </si>
+  <si>
+    <t>260125#HOME-CAMERA-BAK-1137G-2</t>
+  </si>
+  <si>
+    <t>250901-260124
+家庭监控视频备份</t>
+  </si>
+  <si>
+    <t>1137 GB</t>
+  </si>
+  <si>
+    <t>250718#000132L5-1</t>
+  </si>
+  <si>
+    <t>220711#GUANYI-TG-BAK-3-PART2</t>
+  </si>
+  <si>
+    <t>220711 部分视频TG云存储 + Camera Video 
+Channel
+监控备份 第二部分</t>
+  </si>
+  <si>
+    <t>250718#000062L5-1</t>
   </si>
 </sst>
 </file>
@@ -1514,11 +1560,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K278"/>
+  <dimension ref="A1:K279"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="31.55" customWidth="1"/>
-    <col min="3" max="3" width="25.6" customWidth="1"/>
+    <col min="3" max="3" width="26.5" customWidth="1"/>
     <col min="4" max="4" width="15.8083333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.8916666666667" customWidth="1"/>
     <col min="6" max="6" width="21.4916666666667" customWidth="1"/>
@@ -2147,31 +2193,33 @@
         <v>91</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>93</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="H21" s="5"/>
       <c r="I21" s="5">
         <v>46045</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K21" s="4"/>
     </row>
-    <row r="22" ht="36" customHeight="1" spans="1:11">
+    <row r="22" ht="53" customHeight="1" spans="1:11">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
+      <c r="B22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="4" t="s">
-        <v>95</v>
-      </c>
+      <c r="G22" s="4"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5">
         <v>46045</v>
@@ -2179,94 +2227,176 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" ht="36" customHeight="1" spans="1:11">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+    <row r="23" ht="60" customHeight="1" spans="1:11">
+      <c r="A23" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="4"/>
+      <c r="I23" s="5">
+        <v>46046</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" ht="36" customHeight="1" spans="1:11">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
+    <row r="24" ht="56" customHeight="1" spans="1:11">
+      <c r="A24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="4"/>
+      <c r="I24" s="5">
+        <v>46046</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" ht="36" customHeight="1" spans="1:11">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+    <row r="25" ht="59" customHeight="1" spans="1:11">
+      <c r="A25" s="4">
+        <v>17</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="G25" s="4"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5">
+        <v>46046</v>
+      </c>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" ht="36" customHeight="1" spans="1:11">
-      <c r="A26" s="4"/>
+    <row r="26" ht="61" customHeight="1" spans="1:11">
+      <c r="A26" s="4">
+        <v>18</v>
+      </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="5"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="G26" s="4"/>
       <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
+      <c r="I26" s="5">
+        <v>46046</v>
+      </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" ht="36" customHeight="1" spans="1:11">
-      <c r="A27" s="4"/>
+    <row r="27" ht="64" customHeight="1" spans="1:11">
+      <c r="A27" s="4">
+        <v>19</v>
+      </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="5"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="G27" s="4"/>
       <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
+      <c r="I27" s="5">
+        <v>46047</v>
+      </c>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" ht="36" customHeight="1" spans="1:11">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+    <row r="28" ht="64" customHeight="1" spans="1:11">
+      <c r="A28" s="4">
+        <v>20</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="G28" s="4"/>
       <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
+      <c r="I28" s="5">
+        <v>46048</v>
+      </c>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" ht="36" customHeight="1" spans="1:11">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="5"/>
+    <row r="29" ht="86" customHeight="1" spans="1:11">
+      <c r="A29" s="4">
+        <v>21</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>109</v>
+      </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
+      <c r="I29" s="5">
+        <v>46073</v>
+      </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
@@ -2488,7 +2618,7 @@
       <c r="G46" s="4"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
-      <c r="J46" s="7"/>
+      <c r="J46" s="4"/>
       <c r="K46" s="4"/>
     </row>
     <row r="47" ht="36" customHeight="1" spans="1:11">
@@ -3347,6 +3477,7 @@
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="7"/>
+      <c r="K112" s="4"/>
     </row>
     <row r="113" ht="36" customHeight="1" spans="1:10">
       <c r="A113" s="4"/>
@@ -5074,6 +5205,7 @@
       <c r="G256" s="4"/>
       <c r="H256" s="5"/>
       <c r="I256" s="5"/>
+      <c r="J256" s="7"/>
     </row>
     <row r="257" ht="36" customHeight="1" spans="1:9">
       <c r="A257" s="4"/>
@@ -5306,27 +5438,44 @@
       <c r="H277" s="5"/>
       <c r="I277" s="5"/>
     </row>
-    <row r="278" ht="36" customHeight="1"/>
+    <row r="278" ht="36" customHeight="1" spans="1:9">
+      <c r="A278" s="4"/>
+      <c r="B278" s="4"/>
+      <c r="C278" s="4"/>
+      <c r="D278" s="5"/>
+      <c r="E278" s="4"/>
+      <c r="F278" s="4"/>
+      <c r="G278" s="4"/>
+      <c r="H278" s="5"/>
+      <c r="I278" s="5"/>
+    </row>
+    <row r="279" ht="36" customHeight="1"/>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="35">
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B25:B27"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C25:C27"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D25:D27"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E25:E27"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="F18:F20"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F24"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="H9:H10"/>
@@ -5334,6 +5483,7 @@
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
     <mergeCell ref="I3:I5"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="I9:I10"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -348,7 +348,22 @@
     <t>250718#000335L5-1</t>
   </si>
   <si>
+    <t>1189 GB</t>
+  </si>
+  <si>
+    <t>ae07c1ce8a918f4f8d39fab1939a414237c99363484ed31765b44be4972216be</t>
+  </si>
+  <si>
     <t>250718#000383L5-1</t>
+  </si>
+  <si>
+    <t>1244 GB</t>
+  </si>
+  <si>
+    <t>ad60341762c0e3e112c7d882ee0bae914fe4d90ef39057f5f1bf3bb66a629dd3</t>
+  </si>
+  <si>
+    <t>250718#000116L5-1</t>
   </si>
   <si>
     <t>260125#HOME-CAMERA-BAK-1137G-2</t>
@@ -2302,12 +2317,18 @@
       <c r="F25" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="5"/>
+      <c r="G25" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>102</v>
+      </c>
       <c r="I25" s="5">
         <v>46046</v>
       </c>
-      <c r="J25" s="4"/>
+      <c r="J25" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="K25" s="4"/>
     </row>
     <row r="26" ht="61" customHeight="1" spans="1:11">
@@ -2319,14 +2340,20 @@
       <c r="D26" s="5"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="5"/>
+        <v>104</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="I26" s="5">
         <v>46046</v>
       </c>
-      <c r="J26" s="4"/>
+      <c r="J26" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="K26" s="4"/>
     </row>
     <row r="27" ht="64" customHeight="1" spans="1:11">
@@ -2338,12 +2365,12 @@
       <c r="D27" s="5"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
@@ -2353,19 +2380,19 @@
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="5"/>
@@ -2380,17 +2407,17 @@
         <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="121">
   <si>
     <t>#</t>
   </si>
@@ -311,10 +311,13 @@
 2026-01-23</t>
   </si>
   <si>
-    <t>541 GB</t>
+    <t>560 GB</t>
   </si>
   <si>
     <t>250718#000197L5-1</t>
+  </si>
+  <si>
+    <t>874 GB</t>
   </si>
   <si>
     <t>bec0d39515fe7e5e676cf6787921dbc5354b4659c0b872adf4abfa13d27be036</t>
@@ -327,12 +330,21 @@
 手机第 2 次数据备份</t>
   </si>
   <si>
+    <t>368 GB</t>
+  </si>
+  <si>
+    <t>33849cb9ed7539b3ef5ddfa60c0b4b5540364ba5cd65deca63110911531858c7</t>
+  </si>
+  <si>
     <t>* 15</t>
   </si>
   <si>
     <t>250718#000108L5-1</t>
   </si>
   <si>
+    <t>7549f164482563bac3f31b2653061e7a48366d23a1ad87a5b4d77b67d39f931b</t>
+  </si>
+  <si>
     <t>* 16</t>
   </si>
   <si>
@@ -364,6 +376,12 @@
   </si>
   <si>
     <t>250718#000116L5-1</t>
+  </si>
+  <si>
+    <t>524 GB</t>
+  </si>
+  <si>
+    <t>2a8776d24cc0a253baa586af43ab38b33fef42b6f70fb39b6cc7ca8b0cb1381e</t>
   </si>
   <si>
     <t>260125#HOME-CAMERA-BAK-1137G-2</t>
@@ -2210,12 +2228,14 @@
       <c r="G21" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="I21" s="5">
         <v>46045</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K21" s="4"/>
     </row>
@@ -2224,33 +2244,39 @@
         <v>16</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="G22" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5">
-        <v>46045</v>
-      </c>
-      <c r="J22" s="4"/>
+        <v>46046</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="K22" s="4"/>
     </row>
     <row r="23" ht="60" customHeight="1" spans="1:11">
       <c r="A23" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>65</v>
@@ -2259,36 +2285,42 @@
         <v>90</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="I23" s="5">
         <v>46046</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K23" s="4"/>
     </row>
     <row r="24" ht="56" customHeight="1" spans="1:11">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="G24" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5">
         <v>46046</v>
@@ -2303,31 +2335,31 @@
         <v>17</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I25" s="5">
         <v>46046</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K25" s="4"/>
     </row>
@@ -2340,19 +2372,19 @@
       <c r="D26" s="5"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I26" s="5">
         <v>46046</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K26" s="4"/>
     </row>
@@ -2365,14 +2397,20 @@
       <c r="D27" s="5"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="5"/>
+        <v>111</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="I27" s="5">
         <v>46046</v>
       </c>
-      <c r="J27" s="4"/>
+      <c r="J27" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="K27" s="4"/>
     </row>
     <row r="28" ht="64" customHeight="1" spans="1:11">
@@ -2380,19 +2418,19 @@
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="5"/>
@@ -2407,17 +2445,17 @@
         <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="5"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="123">
   <si>
     <t>#</t>
   </si>
@@ -391,17 +391,22 @@
 家庭监控视频备份</t>
   </si>
   <si>
-    <t>1137 GB</t>
+    <t>685 GB</t>
   </si>
   <si>
     <t>250718#000132L5-1</t>
   </si>
   <si>
+    <t>684 GB</t>
+  </si>
+  <si>
+    <t>5bfaf32d8d11085810674cea863470a401d6abe8c965c9de1809f98b9c91d7e6</t>
+  </si>
+  <si>
     <t>220711#GUANYI-TG-BAK-3-PART2</t>
   </si>
   <si>
-    <t>220711 部分视频TG云存储 + Camera Video 
-Channel
+    <t>220711 部分视频TG云存储
 监控备份 第二部分</t>
   </si>
   <si>
@@ -2432,46 +2437,54 @@
       <c r="F28" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="5"/>
+      <c r="G28" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>118</v>
+      </c>
       <c r="I28" s="5">
-        <v>46048</v>
-      </c>
-      <c r="J28" s="4"/>
+        <v>46047</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" ht="86" customHeight="1" spans="1:11">
+    <row r="29" ht="68" customHeight="1" spans="1:11">
       <c r="A29" s="4">
         <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E29" s="4"/>
-      <c r="F29" s="4" t="s">
-        <v>120</v>
-      </c>
+      <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5">
-        <v>46073</v>
+        <v>46055</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" ht="36" customHeight="1" spans="1:11">
-      <c r="A30" s="4"/>
+    <row r="30" ht="58" customHeight="1" spans="1:11">
+      <c r="A30" s="4">
+        <v>22</v>
+      </c>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="5"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>122</v>
+      </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
@@ -5516,7 +5529,7 @@
     </row>
     <row r="279" ht="36" customHeight="1"/>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="36">
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B10:B11"/>
@@ -5541,6 +5554,7 @@
     <mergeCell ref="F18:F20"/>
     <mergeCell ref="F21:F22"/>
     <mergeCell ref="F23:F24"/>
+    <mergeCell ref="F28:F29"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="H9:H10"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="126">
   <si>
     <t>#</t>
   </si>
@@ -408,6 +408,15 @@
   <si>
     <t>220711 部分视频TG云存储
 监控备份 第二部分</t>
+  </si>
+  <si>
+    <t>480 GB</t>
+  </si>
+  <si>
+    <t>385 GB</t>
+  </si>
+  <si>
+    <t>7f6d93d384d16e5461b196db35d8d36cf2d57c9f118a35bc6485c9897cf91fd2</t>
   </si>
   <si>
     <t>250718#000062L5-1</t>
@@ -2464,14 +2473,22 @@
       <c r="D29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>122</v>
+      </c>
       <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="5"/>
+      <c r="G29" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>123</v>
+      </c>
       <c r="I29" s="5">
-        <v>46055</v>
-      </c>
-      <c r="J29" s="4"/>
+        <v>46054</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="K29" s="4"/>
     </row>
     <row r="30" ht="58" customHeight="1" spans="1:11">
@@ -2483,7 +2500,7 @@
       <c r="D30" s="5"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="5"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="134">
   <si>
     <t>#</t>
   </si>
@@ -317,7 +317,7 @@
     <t>250718#000197L5-1</t>
   </si>
   <si>
-    <t>874 GB</t>
+    <t>989 GB</t>
   </si>
   <si>
     <t>bec0d39515fe7e5e676cf6787921dbc5354b4659c0b872adf4abfa13d27be036</t>
@@ -336,6 +336,20 @@
     <t>33849cb9ed7539b3ef5ddfa60c0b4b5540364ba5cd65deca63110911531858c7</t>
   </si>
   <si>
+    <t>260123#JIGE-NVME-1T-DIFF-1</t>
+  </si>
+  <si>
+    <t>机械革命 1T 系统盘差异备份
+系统盘备份数据日期
+2026-02-24</t>
+  </si>
+  <si>
+    <t>123 GB</t>
+  </si>
+  <si>
+    <t>1b62f26a8741a5f010b97eda40bdaa5f4ba0ff441a5b23274177c8a4a7efd61b</t>
+  </si>
+  <si>
     <t>* 15</t>
   </si>
   <si>
@@ -348,6 +362,9 @@
     <t>* 16</t>
   </si>
   <si>
+    <t>* 17</t>
+  </si>
+  <si>
     <t>260124#ST4000NE001-HDD-2-4T-2</t>
   </si>
   <si>
@@ -382,6 +399,18 @@
   </si>
   <si>
     <t>2a8776d24cc0a253baa586af43ab38b33fef42b6f70fb39b6cc7ca8b0cb1381e</t>
+  </si>
+  <si>
+    <t>260224#M2L-BACKUP-260224-385G</t>
+  </si>
+  <si>
+    <t>Mai2Link 260224 数据备份</t>
+  </si>
+  <si>
+    <t>385 GB</t>
+  </si>
+  <si>
+    <t>15d8eff13a82f2066a3c8b9df08af35ce29e64cfe41334df853e9fa7ae60aa30</t>
   </si>
   <si>
     <t>260125#HOME-CAMERA-BAK-1137G-2</t>
@@ -397,7 +426,7 @@
     <t>250718#000132L5-1</t>
   </si>
   <si>
-    <t>684 GB</t>
+    <t>1069 GB</t>
   </si>
   <si>
     <t>5bfaf32d8d11085810674cea863470a401d6abe8c965c9de1809f98b9c91d7e6</t>
@@ -411,9 +440,6 @@
   </si>
   <si>
     <t>480 GB</t>
-  </si>
-  <si>
-    <t>385 GB</t>
   </si>
   <si>
     <t>7f6d93d384d16e5461b196db35d8d36cf2d57c9f118a35bc6485c9897cf91fd2</t>
@@ -1607,11 +1633,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K279"/>
+  <dimension ref="A1:K282"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="31.55" customWidth="1"/>
-    <col min="3" max="3" width="26.5" customWidth="1"/>
+    <col min="3" max="3" width="28.3083333333333" customWidth="1"/>
     <col min="4" max="4" width="15.8083333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.8916666666667" customWidth="1"/>
     <col min="6" max="6" width="21.4916666666667" customWidth="1"/>
@@ -2026,9 +2052,7 @@
         <v>43</v>
       </c>
       <c r="H14" s="5"/>
-      <c r="I14" s="5">
-        <v>45867</v>
-      </c>
+      <c r="I14" s="5"/>
       <c r="J14" s="4" t="s">
         <v>68</v>
       </c>
@@ -2088,9 +2112,7 @@
         <v>54</v>
       </c>
       <c r="H16" s="5"/>
-      <c r="I16" s="5">
-        <v>45867</v>
-      </c>
+      <c r="I16" s="5"/>
       <c r="J16" s="4" t="s">
         <v>71</v>
       </c>
@@ -2155,7 +2177,7 @@
         <v>78</v>
       </c>
       <c r="I18" s="5">
-        <v>45892</v>
+        <v>45901</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>79</v>
@@ -2183,9 +2205,7 @@
         <v>82</v>
       </c>
       <c r="H19" s="5"/>
-      <c r="I19" s="5">
-        <v>45901</v>
-      </c>
+      <c r="I19" s="5"/>
       <c r="J19" s="4" t="s">
         <v>83</v>
       </c>
@@ -2212,9 +2232,7 @@
         <v>86</v>
       </c>
       <c r="H20" s="5"/>
-      <c r="I20" s="5">
-        <v>45901</v>
-      </c>
+      <c r="I20" s="5"/>
       <c r="J20" s="4" t="s">
         <v>87</v>
       </c>
@@ -2246,7 +2264,7 @@
         <v>92</v>
       </c>
       <c r="I21" s="5">
-        <v>46045</v>
+        <v>46077</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>93</v>
@@ -2274,273 +2292,307 @@
         <v>96</v>
       </c>
       <c r="H22" s="5"/>
-      <c r="I22" s="5">
-        <v>46046</v>
-      </c>
+      <c r="I22" s="5"/>
       <c r="J22" s="4" t="s">
         <v>97</v>
       </c>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" ht="60" customHeight="1" spans="1:11">
-      <c r="A23" s="4" t="s">
-        <v>98</v>
+    <row r="23" ht="71" customHeight="1" spans="1:11">
+      <c r="A23" s="4">
+        <v>17</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>98</v>
+      <c r="C23" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>99</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I23" s="5">
-        <v>46046</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" ht="56" customHeight="1" spans="1:11">
+    <row r="24" ht="60" customHeight="1" spans="1:11">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I24" s="5">
+        <v>46077</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="4"/>
+    </row>
+    <row r="25" ht="56" customHeight="1" spans="1:11">
+      <c r="A25" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4" t="s">
+      <c r="F25" s="4"/>
+      <c r="G25" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5">
-        <v>46046</v>
-      </c>
-      <c r="J24" s="4" t="s">
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K24" s="4"/>
-    </row>
-    <row r="25" ht="59" customHeight="1" spans="1:11">
-      <c r="A25" s="4">
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" ht="59" customHeight="1" spans="1:11">
+      <c r="A26" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" ht="59" customHeight="1" spans="1:11">
+      <c r="A27" s="4">
         <v>17</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="B27" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="I25" s="5">
-        <v>46046</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="K25" s="4"/>
-    </row>
-    <row r="26" ht="61" customHeight="1" spans="1:11">
-      <c r="A26" s="4">
-        <v>18</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I26" s="5">
-        <v>46046</v>
-      </c>
-      <c r="J26" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="K26" s="4"/>
-    </row>
-    <row r="27" ht="64" customHeight="1" spans="1:11">
-      <c r="A27" s="4">
-        <v>19</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>112</v>
-      </c>
       <c r="H27" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I27" s="5">
         <v>46046</v>
       </c>
       <c r="J27" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" ht="61" customHeight="1" spans="1:11">
+      <c r="A28" s="4">
+        <v>18</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="K27" s="4"/>
-    </row>
-    <row r="28" ht="64" customHeight="1" spans="1:11">
-      <c r="A28" s="4">
+      <c r="G28" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="5">
+        <v>46046</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" ht="64" customHeight="1" spans="1:11">
+      <c r="A29" s="4">
+        <v>19</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I29" s="5">
+        <v>46077</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" ht="64" customHeight="1" spans="1:11">
+      <c r="A30" s="4">
         <v>20</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="B30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="I28" s="5">
-        <v>46047</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="K28" s="4"/>
-    </row>
-    <row r="29" ht="68" customHeight="1" spans="1:11">
-      <c r="A29" s="4">
-        <v>21</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="E30" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="I29" s="5">
-        <v>46054</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="K29" s="4"/>
-    </row>
-    <row r="30" ht="58" customHeight="1" spans="1:11">
-      <c r="A30" s="4">
-        <v>22</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="G30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
-      <c r="J30" s="4"/>
+      <c r="J30" s="4" t="s">
+        <v>122</v>
+      </c>
       <c r="K30" s="4"/>
     </row>
-    <row r="31" ht="36" customHeight="1" spans="1:11">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="4"/>
+    <row r="31" ht="64" customHeight="1" spans="1:11">
+      <c r="A31" s="4">
+        <v>21</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I31" s="5">
+        <v>46054</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" ht="36" customHeight="1" spans="1:11">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="4"/>
+    <row r="32" ht="68" customHeight="1" spans="1:11">
+      <c r="A32" s="4">
+        <v>22</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="G32" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="4"/>
+      <c r="J32" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="K32" s="4"/>
     </row>
-    <row r="33" ht="36" customHeight="1" spans="1:11">
-      <c r="A33" s="4"/>
+    <row r="33" ht="58" customHeight="1" spans="1:11">
+      <c r="A33" s="4">
+        <v>23</v>
+      </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="5"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+      <c r="F33" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="G33" s="4"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -2726,7 +2778,7 @@
       <c r="G47" s="4"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
-      <c r="J47" s="7"/>
+      <c r="J47" s="4"/>
       <c r="K47" s="4"/>
     </row>
     <row r="48" ht="36" customHeight="1" spans="1:11">
@@ -2739,7 +2791,7 @@
       <c r="G48" s="4"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
-      <c r="J48" s="7"/>
+      <c r="J48" s="4"/>
       <c r="K48" s="4"/>
     </row>
     <row r="49" ht="36" customHeight="1" spans="1:11">
@@ -2752,7 +2804,7 @@
       <c r="G49" s="4"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
-      <c r="J49" s="7"/>
+      <c r="J49" s="4"/>
       <c r="K49" s="4"/>
     </row>
     <row r="50" ht="36" customHeight="1" spans="1:11">
@@ -3574,7 +3626,7 @@
       <c r="J112" s="7"/>
       <c r="K112" s="4"/>
     </row>
-    <row r="113" ht="36" customHeight="1" spans="1:10">
+    <row r="113" ht="36" customHeight="1" spans="1:11">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -3585,8 +3637,9 @@
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="7"/>
-    </row>
-    <row r="114" ht="36" customHeight="1" spans="1:10">
+      <c r="K113" s="4"/>
+    </row>
+    <row r="114" ht="36" customHeight="1" spans="1:11">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -3597,8 +3650,9 @@
       <c r="H114" s="5"/>
       <c r="I114" s="5"/>
       <c r="J114" s="7"/>
-    </row>
-    <row r="115" ht="36" customHeight="1" spans="1:10">
+      <c r="K114" s="4"/>
+    </row>
+    <row r="115" ht="36" customHeight="1" spans="1:11">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -3609,8 +3663,9 @@
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="7"/>
-    </row>
-    <row r="116" ht="36" customHeight="1" spans="1:10">
+      <c r="K115" s="4"/>
+    </row>
+    <row r="116" ht="36" customHeight="1" spans="1:11">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -3622,7 +3677,7 @@
       <c r="I116" s="5"/>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" ht="36" customHeight="1" spans="1:10">
+    <row r="117" ht="36" customHeight="1" spans="1:11">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -3634,7 +3689,7 @@
       <c r="I117" s="5"/>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" ht="36" customHeight="1" spans="1:10">
+    <row r="118" ht="36" customHeight="1" spans="1:11">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -3646,7 +3701,7 @@
       <c r="I118" s="5"/>
       <c r="J118" s="7"/>
     </row>
-    <row r="119" ht="36" customHeight="1" spans="1:10">
+    <row r="119" ht="36" customHeight="1" spans="1:11">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -3658,7 +3713,7 @@
       <c r="I119" s="5"/>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" ht="36" customHeight="1" spans="1:10">
+    <row r="120" ht="36" customHeight="1" spans="1:11">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -3670,7 +3725,7 @@
       <c r="I120" s="5"/>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" ht="36" customHeight="1" spans="1:10">
+    <row r="121" ht="36" customHeight="1" spans="1:11">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -3682,7 +3737,7 @@
       <c r="I121" s="5"/>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" ht="36" customHeight="1" spans="1:10">
+    <row r="122" ht="36" customHeight="1" spans="1:11">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -3694,7 +3749,7 @@
       <c r="I122" s="5"/>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" ht="36" customHeight="1" spans="1:10">
+    <row r="123" ht="36" customHeight="1" spans="1:11">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -3706,7 +3761,7 @@
       <c r="I123" s="5"/>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" ht="36" customHeight="1" spans="1:10">
+    <row r="124" ht="36" customHeight="1" spans="1:11">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -3718,7 +3773,7 @@
       <c r="I124" s="5"/>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" ht="36" customHeight="1" spans="1:10">
+    <row r="125" ht="36" customHeight="1" spans="1:11">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -3730,7 +3785,7 @@
       <c r="I125" s="5"/>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" ht="36" customHeight="1" spans="1:10">
+    <row r="126" ht="36" customHeight="1" spans="1:11">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -3742,7 +3797,7 @@
       <c r="I126" s="5"/>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" ht="36" customHeight="1" spans="1:10">
+    <row r="127" ht="36" customHeight="1" spans="1:11">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -3754,7 +3809,7 @@
       <c r="I127" s="5"/>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" ht="36" customHeight="1" spans="1:10">
+    <row r="128" ht="36" customHeight="1" spans="1:11">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -5302,7 +5357,7 @@
       <c r="I256" s="5"/>
       <c r="J256" s="7"/>
     </row>
-    <row r="257" ht="36" customHeight="1" spans="1:9">
+    <row r="257" ht="36" customHeight="1" spans="1:10">
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -5312,8 +5367,9 @@
       <c r="G257" s="4"/>
       <c r="H257" s="5"/>
       <c r="I257" s="5"/>
-    </row>
-    <row r="258" ht="36" customHeight="1" spans="1:9">
+      <c r="J257" s="7"/>
+    </row>
+    <row r="258" ht="36" customHeight="1" spans="1:10">
       <c r="A258" s="4"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -5323,8 +5379,9 @@
       <c r="G258" s="4"/>
       <c r="H258" s="5"/>
       <c r="I258" s="5"/>
-    </row>
-    <row r="259" ht="36" customHeight="1" spans="1:9">
+      <c r="J258" s="7"/>
+    </row>
+    <row r="259" ht="36" customHeight="1" spans="1:10">
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -5334,8 +5391,9 @@
       <c r="G259" s="4"/>
       <c r="H259" s="5"/>
       <c r="I259" s="5"/>
-    </row>
-    <row r="260" ht="36" customHeight="1" spans="1:9">
+      <c r="J259" s="7"/>
+    </row>
+    <row r="260" ht="36" customHeight="1" spans="1:10">
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -5346,7 +5404,7 @@
       <c r="H260" s="5"/>
       <c r="I260" s="5"/>
     </row>
-    <row r="261" ht="36" customHeight="1" spans="1:9">
+    <row r="261" ht="36" customHeight="1" spans="1:10">
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -5357,7 +5415,7 @@
       <c r="H261" s="5"/>
       <c r="I261" s="5"/>
     </row>
-    <row r="262" ht="36" customHeight="1" spans="1:9">
+    <row r="262" ht="36" customHeight="1" spans="1:10">
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -5368,7 +5426,7 @@
       <c r="H262" s="5"/>
       <c r="I262" s="5"/>
     </row>
-    <row r="263" ht="36" customHeight="1" spans="1:9">
+    <row r="263" ht="36" customHeight="1" spans="1:10">
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -5379,7 +5437,7 @@
       <c r="H263" s="5"/>
       <c r="I263" s="5"/>
     </row>
-    <row r="264" ht="36" customHeight="1" spans="1:9">
+    <row r="264" ht="36" customHeight="1" spans="1:10">
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -5390,7 +5448,7 @@
       <c r="H264" s="5"/>
       <c r="I264" s="5"/>
     </row>
-    <row r="265" ht="36" customHeight="1" spans="1:9">
+    <row r="265" ht="36" customHeight="1" spans="1:10">
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -5401,7 +5459,7 @@
       <c r="H265" s="5"/>
       <c r="I265" s="5"/>
     </row>
-    <row r="266" ht="36" customHeight="1" spans="1:9">
+    <row r="266" ht="36" customHeight="1" spans="1:10">
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -5412,7 +5470,7 @@
       <c r="H266" s="5"/>
       <c r="I266" s="5"/>
     </row>
-    <row r="267" ht="36" customHeight="1" spans="1:9">
+    <row r="267" ht="36" customHeight="1" spans="1:10">
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -5423,7 +5481,7 @@
       <c r="H267" s="5"/>
       <c r="I267" s="5"/>
     </row>
-    <row r="268" ht="36" customHeight="1" spans="1:9">
+    <row r="268" ht="36" customHeight="1" spans="1:10">
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -5434,7 +5492,7 @@
       <c r="H268" s="5"/>
       <c r="I268" s="5"/>
     </row>
-    <row r="269" ht="36" customHeight="1" spans="1:9">
+    <row r="269" ht="36" customHeight="1" spans="1:10">
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -5445,7 +5503,7 @@
       <c r="H269" s="5"/>
       <c r="I269" s="5"/>
     </row>
-    <row r="270" ht="36" customHeight="1" spans="1:9">
+    <row r="270" ht="36" customHeight="1" spans="1:10">
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -5456,7 +5514,7 @@
       <c r="H270" s="5"/>
       <c r="I270" s="5"/>
     </row>
-    <row r="271" ht="36" customHeight="1" spans="1:9">
+    <row r="271" ht="36" customHeight="1" spans="1:10">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -5467,7 +5525,7 @@
       <c r="H271" s="5"/>
       <c r="I271" s="5"/>
     </row>
-    <row r="272" ht="36" customHeight="1" spans="1:9">
+    <row r="272" ht="36" customHeight="1" spans="1:10">
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -5544,45 +5602,88 @@
       <c r="H278" s="5"/>
       <c r="I278" s="5"/>
     </row>
-    <row r="279" ht="36" customHeight="1"/>
+    <row r="279" ht="36" customHeight="1" spans="1:9">
+      <c r="A279" s="4"/>
+      <c r="B279" s="4"/>
+      <c r="C279" s="4"/>
+      <c r="D279" s="5"/>
+      <c r="E279" s="4"/>
+      <c r="F279" s="4"/>
+      <c r="G279" s="4"/>
+      <c r="H279" s="5"/>
+      <c r="I279" s="5"/>
+    </row>
+    <row r="280" ht="36" customHeight="1" spans="1:9">
+      <c r="A280" s="4"/>
+      <c r="B280" s="4"/>
+      <c r="C280" s="4"/>
+      <c r="D280" s="5"/>
+      <c r="E280" s="4"/>
+      <c r="F280" s="4"/>
+      <c r="G280" s="4"/>
+      <c r="H280" s="5"/>
+      <c r="I280" s="5"/>
+    </row>
+    <row r="281" ht="36" customHeight="1" spans="1:9">
+      <c r="A281" s="4"/>
+      <c r="B281" s="4"/>
+      <c r="C281" s="4"/>
+      <c r="D281" s="5"/>
+      <c r="E281" s="4"/>
+      <c r="F281" s="4"/>
+      <c r="G281" s="4"/>
+      <c r="H281" s="5"/>
+      <c r="I281" s="5"/>
+    </row>
+    <row r="282" ht="36" customHeight="1"/>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="46">
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B27:B29"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="C27:C29"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="D27:D29"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="E27:E29"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="F18:F20"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F31:F32"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="H15:H16"/>
     <mergeCell ref="H18:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
     <mergeCell ref="I3:I5"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
